--- a/artfynd/A 28435-2022 artfynd.xlsx
+++ b/artfynd/A 28435-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28435-2022 artfynd.xlsx
+++ b/artfynd/A 28435-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>103800482</v>
       </c>
       <c r="B2" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543025.2954530147</v>
+        <v>543025</v>
       </c>
       <c r="R2" t="n">
-        <v>6648896.099539751</v>
+        <v>6648896</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,6 +770,323 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>96255654</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fagersta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>543055</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6648868</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>106032028</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kopängsberget, Hedkärra, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>543080</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6648881</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4566163</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99771</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222302</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spädstarr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carex disperma</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Dewey</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>V om järnvägen, intill Kopängsbergets N-branter 500 m VSV sjön Eskiln, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>543127</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6648916</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1994-06-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1994-06-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikliga förekomster över stora ytor.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Rikkärr</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Uppföljning av skyddade områden</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28435-2022 artfynd.xlsx
+++ b/artfynd/A 28435-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103800482</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -869,6 +879,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96255654</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032028</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,8 +1107,19 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4566163</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>